--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_individual_h_10.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_individual_h_10.xlsx
@@ -658,7 +658,7 @@
         <v>0.008511962878429835</v>
       </c>
       <c r="C2" t="n">
-        <v>63129780</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>63129780</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>43845785</v>
+        <v>3924814</v>
       </c>
       <c r="L2" t="n">
-        <v>23538735</v>
+        <v>1792737</v>
       </c>
       <c r="M2" t="n">
-        <v>5549396</v>
+        <v>349317</v>
       </c>
       <c r="N2" t="n">
-        <v>243868</v>
+        <v>6303</v>
       </c>
       <c r="O2" t="n">
-        <v>3271175</v>
+        <v>179730</v>
       </c>
       <c r="P2" t="n">
-        <v>1241213</v>
+        <v>57371</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999759197235107</v>
+        <v>0.9999898672103882</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8453686237335205</v>
+        <v>0.740313708782196</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7205420136451721</v>
+        <v>0.5468462705612183</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6520390510559082</v>
+        <v>0.4184128642082214</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2601253092288971</v>
+        <v>0.0496893934905529</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7016927003860474</v>
+        <v>0.4672377407550812</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8162872791290283</v>
+        <v>0.635281503200531</v>
       </c>
       <c r="X2" t="n">
-        <v>63129780</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>63129780</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>47949558</v>
+        <v>4750163</v>
       </c>
       <c r="AG2" t="n">
-        <v>29849211</v>
+        <v>3018205</v>
       </c>
       <c r="AH2" t="n">
-        <v>8017135</v>
+        <v>806591</v>
       </c>
       <c r="AI2" t="n">
-        <v>590732</v>
+        <v>59281</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4597593</v>
+        <v>461241</v>
       </c>
       <c r="AK2" t="n">
-        <v>1801493</v>
+        <v>180417</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9559409618377686</v>
+        <v>0.9546809196472168</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9116660952568054</v>
+        <v>0.9128581881523132</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582287430763245</v>
+        <v>0.8581860065460205</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6617533564567566</v>
+        <v>0.6609027981758118</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.902009129524231</v>
+        <v>0.901951789855957</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314513206481934</v>
+        <v>0.9314922094345093</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002039737086905555</v>
       </c>
       <c r="C3" t="n">
-        <v>1078</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>43845785</v>
+        <v>3924814</v>
       </c>
       <c r="E3" t="n">
-        <v>6037574</v>
+        <v>986777</v>
       </c>
       <c r="F3" t="n">
-        <v>166902</v>
+        <v>42787</v>
       </c>
       <c r="G3" t="n">
-        <v>13907</v>
+        <v>2995</v>
       </c>
       <c r="H3" t="n">
-        <v>9897</v>
+        <v>2500</v>
       </c>
       <c r="I3" t="n">
-        <v>597</v>
+        <v>217</v>
       </c>
       <c r="J3" t="n">
-        <v>100164700</v>
+        <v>10016558</v>
       </c>
       <c r="K3" t="n">
-        <v>105200168</v>
+        <v>9992747</v>
       </c>
       <c r="L3" t="n">
-        <v>121357321</v>
+        <v>11524885</v>
       </c>
       <c r="M3" t="n">
-        <v>150982009</v>
+        <v>14902199</v>
       </c>
       <c r="N3" t="n">
-        <v>161708802</v>
+        <v>16119247</v>
       </c>
       <c r="O3" t="n">
-        <v>156804911</v>
+        <v>15612756</v>
       </c>
       <c r="P3" t="n">
-        <v>161082041</v>
+        <v>16102858</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8755893707275391</v>
+        <v>0.7912752628326416</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7174404859542847</v>
+        <v>0.5401222109794617</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5933562517166138</v>
+        <v>0.3708815276622772</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2729161083698273</v>
+        <v>0.07018305361270905</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6413527727127075</v>
+        <v>0.3510975539684296</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6415820717811584</v>
+        <v>0.296024352312088</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>47949558</v>
+        <v>4750163</v>
       </c>
       <c r="Z3" t="n">
-        <v>1972670</v>
+        <v>194702</v>
       </c>
       <c r="AA3" t="n">
-        <v>84826</v>
+        <v>8398</v>
       </c>
       <c r="AB3" t="n">
-        <v>68106</v>
+        <v>6808</v>
       </c>
       <c r="AC3" t="n">
-        <v>280</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>100166220</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>111010280</v>
+        <v>11143996</v>
       </c>
       <c r="AG3" t="n">
-        <v>127594505</v>
+        <v>12722349</v>
       </c>
       <c r="AH3" t="n">
-        <v>152619092</v>
+        <v>15254456</v>
       </c>
       <c r="AI3" t="n">
-        <v>162100491</v>
+        <v>16209376</v>
       </c>
       <c r="AJ3" t="n">
-        <v>157696105</v>
+        <v>15767551</v>
       </c>
       <c r="AK3" t="n">
-        <v>161228809</v>
+        <v>16122526</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575406908988953</v>
+        <v>0.9576725363731384</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097784161567688</v>
+        <v>0.9093356132507324</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.85721355676651</v>
+        <v>0.8563846349716187</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.661096453666687</v>
+        <v>0.6600859761238098</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014128446578979</v>
+        <v>0.9010214805603027</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311903715133667</v>
+        <v>0.9309202432632446</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.0321438545796774</v>
       </c>
       <c r="C4" t="n">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>7436947</v>
+        <v>1245241</v>
       </c>
       <c r="E4" t="n">
-        <v>23538735</v>
+        <v>1792737</v>
       </c>
       <c r="F4" t="n">
-        <v>1568197</v>
+        <v>230170</v>
       </c>
       <c r="G4" t="n">
-        <v>89477</v>
+        <v>17649</v>
       </c>
       <c r="H4" t="n">
-        <v>160990</v>
+        <v>30264</v>
       </c>
       <c r="I4" t="n">
-        <v>14869</v>
+        <v>3064</v>
       </c>
       <c r="J4" t="n">
-        <v>1520</v>
+        <v>64</v>
       </c>
       <c r="K4" t="n">
-        <v>8020092</v>
+        <v>1376741</v>
       </c>
       <c r="L4" t="n">
-        <v>9129359</v>
+        <v>1485583</v>
       </c>
       <c r="M4" t="n">
-        <v>2961438</v>
+        <v>485545</v>
       </c>
       <c r="N4" t="n">
-        <v>693634</v>
+        <v>120545</v>
       </c>
       <c r="O4" t="n">
-        <v>1390659</v>
+        <v>204935</v>
       </c>
       <c r="P4" t="n">
-        <v>279346</v>
+        <v>32937</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999879598617554</v>
+        <v>0.9999949336051941</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8602136969566345</v>
+        <v>0.7649466395378113</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7189878821372986</v>
+        <v>0.5434634685516357</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6213151216506958</v>
+        <v>0.3932160437107086</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2663672566413879</v>
+        <v>0.05818440392613411</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6701672673225403</v>
+        <v>0.4009262025356293</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7184666991233826</v>
+        <v>0.4038604199886322</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2063963</v>
+        <v>210743</v>
       </c>
       <c r="Z4" t="n">
-        <v>29849211</v>
+        <v>3018205</v>
       </c>
       <c r="AA4" t="n">
-        <v>828823</v>
+        <v>83377</v>
       </c>
       <c r="AB4" t="n">
-        <v>55262</v>
+        <v>5608</v>
       </c>
       <c r="AC4" t="n">
-        <v>11381</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>680</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2209980</v>
+        <v>225492</v>
       </c>
       <c r="AG4" t="n">
-        <v>2892175</v>
+        <v>288119</v>
       </c>
       <c r="AH4" t="n">
-        <v>1324355</v>
+        <v>133288</v>
       </c>
       <c r="AI4" t="n">
-        <v>301945</v>
+        <v>30416</v>
       </c>
       <c r="AJ4" t="n">
-        <v>499465</v>
+        <v>50140</v>
       </c>
       <c r="AK4" t="n">
-        <v>132578</v>
+        <v>13269</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9567400813102722</v>
+        <v>0.956174373626709</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9107212424278259</v>
+        <v>0.9110934734344482</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8577207922935486</v>
+        <v>0.8572843670845032</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6614247560501099</v>
+        <v>0.6604941487312317</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017109274864197</v>
+        <v>0.9014863967895508</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.93132084608078</v>
+        <v>0.9312061071395874</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>413837</v>
+        <v>97531</v>
       </c>
       <c r="E5" t="n">
-        <v>2524226</v>
+        <v>381423</v>
       </c>
       <c r="F5" t="n">
-        <v>5549396</v>
+        <v>349317</v>
       </c>
       <c r="G5" t="n">
-        <v>220511</v>
+        <v>32454</v>
       </c>
       <c r="H5" t="n">
-        <v>586177</v>
+        <v>71582</v>
       </c>
       <c r="I5" t="n">
-        <v>58338</v>
+        <v>9535</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6229955</v>
+        <v>1035298</v>
       </c>
       <c r="L5" t="n">
-        <v>9270585</v>
+        <v>1526395</v>
       </c>
       <c r="M5" t="n">
-        <v>3803157</v>
+        <v>592539</v>
       </c>
       <c r="N5" t="n">
-        <v>649696</v>
+        <v>83505</v>
       </c>
       <c r="O5" t="n">
-        <v>1829255</v>
+        <v>332179</v>
       </c>
       <c r="P5" t="n">
-        <v>693400</v>
+        <v>136434</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.999990701675415</v>
+        <v>0.9999960660934448</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9127348661422729</v>
+        <v>0.8522903919219971</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8873215317726135</v>
+        <v>0.8155510425567627</v>
       </c>
       <c r="T5" t="n">
-        <v>0.958574652671814</v>
+        <v>0.9339797496795654</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9917736649513245</v>
+        <v>0.9875043034553528</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9802817106246948</v>
+        <v>0.9671079516410828</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9940430521965027</v>
+        <v>0.9896279573440552</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>80454</v>
+        <v>8120</v>
       </c>
       <c r="Z5" t="n">
-        <v>857060</v>
+        <v>87176</v>
       </c>
       <c r="AA5" t="n">
-        <v>8017135</v>
+        <v>806591</v>
       </c>
       <c r="AB5" t="n">
-        <v>99758</v>
+        <v>10039</v>
       </c>
       <c r="AC5" t="n">
-        <v>291816</v>
+        <v>29297</v>
       </c>
       <c r="AD5" t="n">
-        <v>6330</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2126182</v>
+        <v>209949</v>
       </c>
       <c r="AG5" t="n">
-        <v>2960109</v>
+        <v>300927</v>
       </c>
       <c r="AH5" t="n">
-        <v>1335418</v>
+        <v>135265</v>
       </c>
       <c r="AI5" t="n">
-        <v>302832</v>
+        <v>30527</v>
       </c>
       <c r="AJ5" t="n">
-        <v>502837</v>
+        <v>50668</v>
       </c>
       <c r="AK5" t="n">
-        <v>133120</v>
+        <v>13388</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734460115432739</v>
+        <v>0.9733342528343201</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641615152359009</v>
+        <v>0.963927686214447</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837119579315186</v>
+        <v>0.9835542440414429</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962964653968811</v>
+        <v>0.9962679147720337</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938620328903198</v>
+        <v>0.993826687335968</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983729124069214</v>
+        <v>0.9983675479888916</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>134681</v>
+        <v>20896</v>
       </c>
       <c r="E6" t="n">
-        <v>193353</v>
+        <v>25813</v>
       </c>
       <c r="F6" t="n">
-        <v>225353</v>
+        <v>27735</v>
       </c>
       <c r="G6" t="n">
-        <v>243868</v>
+        <v>6303</v>
       </c>
       <c r="H6" t="n">
-        <v>87758</v>
+        <v>8043</v>
       </c>
       <c r="I6" t="n">
-        <v>8465</v>
+        <v>1003</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>65084</v>
+        <v>6593</v>
       </c>
       <c r="Z6" t="n">
-        <v>53535</v>
+        <v>5350</v>
       </c>
       <c r="AA6" t="n">
-        <v>109471</v>
+        <v>11081</v>
       </c>
       <c r="AB6" t="n">
-        <v>590732</v>
+        <v>59281</v>
       </c>
       <c r="AC6" t="n">
-        <v>69932</v>
+        <v>7022</v>
       </c>
       <c r="AD6" t="n">
-        <v>4810</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>33110</v>
+        <v>12316</v>
       </c>
       <c r="E7" t="n">
-        <v>343460</v>
+        <v>82492</v>
       </c>
       <c r="F7" t="n">
-        <v>926594</v>
+        <v>163112</v>
       </c>
       <c r="G7" t="n">
-        <v>328937</v>
+        <v>55141</v>
       </c>
       <c r="H7" t="n">
-        <v>3271175</v>
+        <v>179730</v>
       </c>
       <c r="I7" t="n">
-        <v>197077</v>
+        <v>19118</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>199</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8100</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>297921</v>
+        <v>30099</v>
       </c>
       <c r="AB7" t="n">
-        <v>76159</v>
+        <v>7694</v>
       </c>
       <c r="AC7" t="n">
-        <v>4597593</v>
+        <v>461241</v>
       </c>
       <c r="AD7" t="n">
-        <v>120458</v>
+        <v>12057</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>1517</v>
+        <v>757</v>
       </c>
       <c r="E8" t="n">
-        <v>30746</v>
+        <v>9078</v>
       </c>
       <c r="F8" t="n">
-        <v>74392</v>
+        <v>21741</v>
       </c>
       <c r="G8" t="n">
-        <v>40802</v>
+        <v>12306</v>
       </c>
       <c r="H8" t="n">
-        <v>545837</v>
+        <v>92546</v>
       </c>
       <c r="I8" t="n">
-        <v>1241213</v>
+        <v>57371</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>280</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>810</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3314</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2660</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>126056</v>
+        <v>12679</v>
       </c>
       <c r="AD8" t="n">
-        <v>1801493</v>
+        <v>180417</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
